--- a/tests/fixtures/formatting-testdata/NumberFormats.xlsx
+++ b/tests/fixtures/formatting-testdata/NumberFormats.xlsx
@@ -1,156 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamleshn/workspace/joplin-univer/tests/fixtures/formatting-testdata/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9C460F-CB8B-B64E-BFC6-6C951BAED935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Number Formats" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Number Formats" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
-  <si>
-    <t>Format Name</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Format Code</t>
-  </si>
-  <si>
-    <t>General</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0.00</t>
-  </si>
-  <si>
-    <t>#,##0</t>
-  </si>
-  <si>
-    <t>#,##0.00</t>
-  </si>
-  <si>
-    <t>Currency USD</t>
-  </si>
-  <si>
-    <t>$#,##0.00</t>
-  </si>
-  <si>
-    <t>Currency EUR</t>
-  </si>
-  <si>
-    <t>#,##0.00 "€"</t>
-  </si>
-  <si>
-    <t>Currency SEK</t>
-  </si>
-  <si>
-    <t>_-* #,##0.00 "kr"_-</t>
-  </si>
-  <si>
-    <t>Percent 0%</t>
-  </si>
-  <si>
-    <t>Percent 0.00%</t>
-  </si>
-  <si>
-    <t>Date m/d/yy</t>
-  </si>
-  <si>
-    <t>m/d/yy</t>
-  </si>
-  <si>
-    <t>Date yyyy-mm-dd</t>
-  </si>
-  <si>
-    <t>yyyy-mm-dd</t>
-  </si>
-  <si>
-    <t>Date dd-mmm-yy</t>
-  </si>
-  <si>
-    <t>dd-mmm-yy</t>
-  </si>
-  <si>
-    <t>Date AM/PM</t>
-  </si>
-  <si>
-    <t>[$-409]m/d/yy h:mm AM/PM;@</t>
-  </si>
-  <si>
-    <t>Accounting</t>
-  </si>
-  <si>
-    <t>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</t>
-  </si>
-  <si>
-    <t>Custom text @</t>
-  </si>
-  <si>
-    <t>Hello</t>
-  </si>
-  <si>
-    <t>@ "suffix"</t>
-  </si>
-  <si>
-    <t>Conditional [Red]</t>
-  </si>
-  <si>
-    <t>[Red]#,##0.00;[Blue]#,##0.00</t>
-  </si>
-  <si>
-    <t>0%</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ &quot;kr&quot;_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="168" formatCode="dd\-mmm\-yy"/>
-    <numFmt numFmtId="169" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="170" formatCode="@\ &quot;suffix&quot;"/>
-    <numFmt numFmtId="171" formatCode="[Red]#,##0.00;[Blue]#,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="10">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00 &quot;€&quot;"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00 &quot;kr&quot;_-"/>
+    <numFmt numFmtId="167" formatCode="m/d/yy"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="169" formatCode="dd-mmm-yy"/>
+    <numFmt numFmtId="170" formatCode="[$-409]m/d/yy h:mm AM/PM;@"/>
+    <numFmt numFmtId="171" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="172" formatCode="@ &quot;suffix&quot;"/>
+    <numFmt numFmtId="173" formatCode="[Red]#,##0.00;[Blue]#,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -168,41 +60,98 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -490,211 +439,291 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Format Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Format Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1234.5678</v>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
         <v>1234.5678</v>
       </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>1234.5678</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#,##0</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
         <v>1234.5678</v>
       </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#,##0.00</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>1234.5678</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Currency USD</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>1234.56</v>
       </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Currency EUR</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
         <v>1234.56</v>
       </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>#,##0.00 "€"</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Currency SEK</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
         <v>1234.56</v>
       </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>_-* #,##0.00 "kr"_-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Percent 0%</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
         <v>0.35</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="10">
-        <v>0.35670000000000002</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="11">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Percent 0.00%</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Date m/d/yy</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
         <v>45000</v>
       </c>
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>m/d/yy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Date yyyy-mm-dd</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>yyyy-mm-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Date dd-mmm-yy</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
         <v>45000</v>
       </c>
-      <c r="C14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dd-mmm-yy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Date AM/PM</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
         <v>45000.75</v>
       </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[$-409]m/d/yy h:mm AM/PM;@</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
         <v>1234.56</v>
       </c>
-      <c r="C16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="17">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Custom text @</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Hello</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>@ "suffix"</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Conditional [Red]</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
         <v>-1234.56</v>
       </c>
-      <c r="C18" t="s">
-        <v>30</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[Red]#,##0.00;[Blue]#,##0.00</t>
+        </is>
       </c>
     </row>
   </sheetData>
